--- a/frontend/public/templates/members-import-template.xlsx
+++ b/frontend/public/templates/members-import-template.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3. 头像列用于放图片：可在对应行插入一张头像图片，系统会读取该行第一张图片；头像列里的文字不会被导入。</t>
+          <t>3. 头像列用于放图片：在对应行插入头像后，系统按图片所在行匹配成员；没有照片可以留空。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>4. 展示排序：0 表示不在公开网站展示；大于 0 时按数字从小到大展示。</t>
+          <t>4. 更新已有成员时，头像留空会保留原头像；需要移除原头像时，在头像列填写“清空”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5. 展示排序：0 表示不在公开网站展示；大于 0 时按数字从小到大展示。</t>
         </is>
       </c>
     </row>
